--- a/semana03/calculo_a_mano/interaccion_columna18.xlsx
+++ b/semana03/calculo_a_mano/interaccion_columna18.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcubi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\SAP3000 v1.0\semana03\calculo_a_mano\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5E968C-9003-4962-BF93-D5548BA4436B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1C360A-DD70-490E-BCF7-C5A5595DB97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{4AE65EBE-4BF5-45D0-A603-65D1C8FB30C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elemento 18" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -60,9 +57,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -70,13 +64,196 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="75">
   <si>
+    <t>PREGUNTA 2: DIAGRAMA DE INTERACCIÓN</t>
+  </si>
+  <si>
+    <t>Datos de entrada</t>
+  </si>
+  <si>
+    <t>Demandas elemento 18</t>
+  </si>
+  <si>
+    <t>Caso</t>
+  </si>
+  <si>
+    <t>M [kN m]</t>
+  </si>
+  <si>
+    <t>P [kN]</t>
+  </si>
+  <si>
+    <t>Hormigón</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>fc'</t>
+  </si>
+  <si>
+    <t>Mpa</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>EY</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>mm2</t>
+  </si>
+  <si>
+    <t>ecu</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>Capacidad nominal aproximada con el metodo manual. Las demandas vienen del repositorio, con q_Q = 3.0 kN/m2 (NCh1537 Of.2009 Tabla 4, salas de clases): python semana03/demanda_capacidad.py ingenieria 18</t>
+  </si>
+  <si>
+    <t>Representacion</t>
+  </si>
+  <si>
+    <t>16 barras Ø16 agrupadas en 4 capas equivalentes simetricas.</t>
+  </si>
+  <si>
+    <t>Acero</t>
+  </si>
+  <si>
+    <t>fy</t>
+  </si>
+  <si>
+    <t>Es</t>
+  </si>
+  <si>
+    <t>As1</t>
+  </si>
+  <si>
+    <t>5 barras Ø16</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>As2</t>
+  </si>
+  <si>
+    <t>3 barras Ø16</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>As3</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>As4</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>Ast</t>
+  </si>
+  <si>
+    <t>Punto a. Compresión pura</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>kN</t>
+  </si>
+  <si>
+    <t>M0</t>
+  </si>
+  <si>
+    <t>kN m</t>
+  </si>
+  <si>
+    <t>f Pn</t>
+  </si>
+  <si>
+    <t>f Mn</t>
+  </si>
+  <si>
+    <t>Punto b. Deformación inferior hormigón nula</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>es4</t>
+  </si>
+  <si>
     <t>Fila acero</t>
   </si>
   <si>
+    <t>esi</t>
+  </si>
+  <si>
+    <t>ssi [Mpa]</t>
+  </si>
+  <si>
     <t>Fsi [kN]</t>
   </si>
   <si>
-    <t>Hormigón</t>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Compresión - Fluencia</t>
+  </si>
+  <si>
+    <t>Compresión - No fluencia</t>
+  </si>
+  <si>
+    <t>Punto c. Punto de balance</t>
+  </si>
+  <si>
+    <t>Tracción - No fluencia</t>
+  </si>
+  <si>
+    <t>Tracción - Fluencia</t>
+  </si>
+  <si>
+    <t>Punto d. Transición deformación acero &gt; 0,003</t>
+  </si>
+  <si>
+    <t>Punto e. Última falla dúctil</t>
+  </si>
+  <si>
+    <t>Punto f. Flexión pura</t>
+  </si>
+  <si>
+    <t>Buscar objetivo P0=0 iterando c</t>
+  </si>
+  <si>
+    <t>Punto g. Tracción pura</t>
   </si>
   <si>
     <t>Mn [kN m]</t>
@@ -85,229 +262,10 @@
     <t>Pn [kN]</t>
   </si>
   <si>
-    <t>PREGUNTA 2: DIAGRAMA DE INTERACCIÓN</t>
-  </si>
-  <si>
-    <t>Datos de entrada</t>
-  </si>
-  <si>
-    <t>fc'</t>
-  </si>
-  <si>
-    <t>Mpa</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>mm</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>Ag</t>
-  </si>
-  <si>
-    <t>mm2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>cu</t>
-    </r>
-  </si>
-  <si>
-    <t>Acero</t>
-  </si>
-  <si>
-    <t>fy</t>
-  </si>
-  <si>
-    <t>As1</t>
-  </si>
-  <si>
-    <t>As2</t>
-  </si>
-  <si>
-    <t>As3</t>
-  </si>
-  <si>
-    <t>As4</t>
-  </si>
-  <si>
-    <t>d1</t>
-  </si>
-  <si>
-    <t>d2</t>
-  </si>
-  <si>
-    <t>d3</t>
-  </si>
-  <si>
-    <t>d4</t>
-  </si>
-  <si>
-    <t>Ast</t>
-  </si>
-  <si>
-    <t>Es</t>
-  </si>
-  <si>
-    <t>Punto a. Compresión pura</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>kN</t>
-  </si>
-  <si>
-    <t>kN m</t>
-  </si>
-  <si>
-    <t>Punto b. Deformación inferior hormigón nula</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>si</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>si [Mpa]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">f </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Pn</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">f </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Mn</t>
-    </r>
-  </si>
-  <si>
-    <t>M0</t>
-  </si>
-  <si>
-    <t>Punto c. Punto de balance</t>
-  </si>
-  <si>
-    <r>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>s4</t>
-    </r>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Compresión - Fluencia</t>
-  </si>
-  <si>
-    <t>Compresión - No fluencia</t>
-  </si>
-  <si>
-    <t>Tracción - No fluencia</t>
-  </si>
-  <si>
-    <t>Tracción - Fluencia</t>
-  </si>
-  <si>
-    <t>Punto d. Transición deformación acero &gt; 0,003</t>
-  </si>
-  <si>
-    <t>Punto e. Última falla dúctil</t>
-  </si>
-  <si>
-    <t>Punto f. Flexión pura</t>
-  </si>
-  <si>
-    <t>Punto g. Tracción pura</t>
+    <t>f Mn [kN m]</t>
+  </si>
+  <si>
+    <t>f Pn [kN]</t>
   </si>
   <si>
     <t>a. Compresión pura</t>
@@ -329,102 +287,6 @@
   </si>
   <si>
     <t>g. Tracción pura</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">f </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Mn [kN m]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">f </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Pn</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>[kN]</t>
-    </r>
-  </si>
-  <si>
-    <t>Buscar objetivo P0=0 iterando c</t>
-  </si>
-  <si>
-    <t>5 barras Ø16</t>
-  </si>
-  <si>
-    <t>3 barras Ø16</t>
-  </si>
-  <si>
-    <t>Demandas elemento 18</t>
-  </si>
-  <si>
-    <t>Caso</t>
-  </si>
-  <si>
-    <t>M [kN m]</t>
-  </si>
-  <si>
-    <t>P [kN]</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>EY</t>
-  </si>
-  <si>
-    <t>Nota</t>
-  </si>
-  <si>
-    <t>Capacidad nominal aproximada con el metodo manual; las demandas vienen del repositorio.</t>
-  </si>
-  <si>
-    <t>Representacion</t>
-  </si>
-  <si>
-    <t>16 barras Ø16 agrupadas en 4 capas equivalentes simetricas.</t>
   </si>
 </sst>
 </file>
@@ -432,10 +294,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,12 +324,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -511,7 +367,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -543,33 +399,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -582,16 +451,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -607,7 +476,7 @@
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,26 +489,28 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,15 +533,8 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -679,7 +543,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -703,29 +567,9 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-CL"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -734,7 +578,7 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.12891950747433922"/>
+          <c:x val="0.1289195074743392"/>
           <c:y val="4.6310820736449043E-2"/>
           <c:w val="0.84594743516315341"/>
           <c:h val="0.72525232291169084"/>
@@ -765,9 +609,9 @@
                   <a:lumOff val="40000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -783,8 +627,8 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -886,34 +730,22 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-52A6-496D-A026-099A3337370B}"/>
+              <c16:uniqueId val="{00000000-6AA4-43B5-9AE5-A3B971F1D674}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="18"/>
-          <c:order val="8"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>Demandas elemento 18</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="19050" cap="rnd">
-                  <a:solidFill>
-                    <a:srgbClr val="156082">
-                      <a:lumMod val="80000"/>
-                    </a:srgbClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -924,19 +756,8 @@
               </a:solidFill>
               <a:ln w="9525">
                 <a:noFill/>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-                    <a:solidFill>
-                      <a:srgbClr val="156082">
-                        <a:lumMod val="80000"/>
-                      </a:srgbClr>
-                    </a:solidFill>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -946,16 +767,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>34.6</c:v>
+                  <c:v>34.646799999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.1</c:v>
+                  <c:v>10.626799999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.2</c:v>
+                  <c:v>18.493200000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.799999999999997</c:v>
+                  <c:v>38.708399999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -967,16 +788,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3385.9</c:v>
+                  <c:v>3385.9176000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>684.5</c:v>
+                  <c:v>1026.7221</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8</c:v>
+                  <c:v>5.4977</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50.9</c:v>
+                  <c:v>58.2682</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -984,7 +805,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E557-49CA-BEB3-AEA402E63D9E}"/>
+              <c16:uniqueId val="{00000001-6AA4-43B5-9AE5-A3B971F1D674}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1003,8 +824,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:v>Pn [kN]</c:v>
           </c:tx>
@@ -1019,7 +840,6 @@
               <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -1035,8 +855,8 @@
                 <a:solidFill>
                   <a:schemeClr val="accent5"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
               </a:ln>
-              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -1138,7 +958,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-52A6-496D-A026-099A3337370B}"/>
+              <c16:uniqueId val="{00000002-6AA4-43B5-9AE5-A3B971F1D674}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1152,484 +972,6 @@
         </c:dLbls>
         <c:axId val="36500768"/>
         <c:axId val="36501248"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="12"/>
-                <c:order val="2"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent1">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="tx2"/>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent1">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$190</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$190</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{0000000C-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="13"/>
-                <c:order val="3"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent2">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent2">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent2">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$191</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$191</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{0000000D-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="14"/>
-                <c:order val="4"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent3">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent3">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent3">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$192</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$192</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{0000000E-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="15"/>
-                <c:order val="5"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent4">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent4">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent4">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:dPt>
-                  <c:idx val="0"/>
-                  <c:marker>
-                    <c:symbol val="circle"/>
-                    <c:size val="5"/>
-                    <c:spPr>
-                      <a:solidFill>
-                        <a:schemeClr val="accent1"/>
-                      </a:solidFill>
-                      <a:ln w="9525">
-                        <a:solidFill>
-                          <a:schemeClr val="accent4">
-                            <a:lumMod val="80000"/>
-                            <a:lumOff val="20000"/>
-                          </a:schemeClr>
-                        </a:solidFill>
-                      </a:ln>
-                      <a:effectLst/>
-                    </c:spPr>
-                  </c:marker>
-                  <c:bubble3D val="0"/>
-                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000012-D2D1-4453-8CF1-B3FC0063710F}"/>
-                    </c:ext>
-                  </c:extLst>
-                </c:dPt>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$193</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$193</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{0000000F-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="16"/>
-                <c:order val="6"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent5">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent5">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent5">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$194</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$194</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000010-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="17"/>
-                <c:order val="7"/>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="80000"/>
-                        <a:lumOff val="20000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent6">
-                          <a:lumMod val="80000"/>
-                          <a:lumOff val="20000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$E$195</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Elemento 18'!$C$195</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="1"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000011-D2D1-4453-8CF1-B3FC0063710F}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-          </c:ext>
-        </c:extLst>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="36500768"/>
@@ -1647,9 +989,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -1659,7 +1001,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1691,29 +1033,9 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1728,16 +1050,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1772,9 +1094,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -1784,7 +1106,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1808,29 +1130,9 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
+              <a:prstDash val="solid"/>
             </a:ln>
-            <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1845,16 +1147,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
+            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
-          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1873,13 +1175,6 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -1887,7 +1182,7 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.28482129414485513"/>
+          <c:x val="0.28482129414485508"/>
           <c:y val="0.91035178821825358"/>
           <c:w val="0.55048031030420441"/>
           <c:h val="5.1746100230621858E-2"/>
@@ -1898,15 +1193,15 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:effectLst/>
       </c:spPr>
       <c:txPr>
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1924,14 +1219,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1944,585 +1232,16 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
+      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
-    <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="es-CL"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2542,10 +1261,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D7ABD60-7A44-567B-71BF-F201E52A2A02}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2881,44 +1600,23 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="609" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{1A4D8C8A-EE54-4E37-BA19-F1167BC0BCC5}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;9dfcbba7-a0c4-4723-af7b-a4a342094aad&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E17553-F9AF-4D08-A43A-08B050C2EE60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="4" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="2"/>
-    <col min="4" max="4" width="13.36328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="11.54296875" style="2"/>
+    <col min="2" max="2" width="22.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:12">
@@ -2926,279 +1624,279 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:12">
       <c r="J5" s="2" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2">
-        <v>34.6</v>
+        <v>34.646799999999999</v>
       </c>
       <c r="L6" s="2">
-        <v>3385.9</v>
+        <v>3385.9176000000002</v>
       </c>
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3">
         <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2">
-        <v>7.1</v>
+        <v>10.626799999999999</v>
       </c>
       <c r="L7" s="2">
-        <v>684.5</v>
+        <v>1026.7221</v>
       </c>
     </row>
     <row r="8" spans="2:12">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3">
         <v>500</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K8" s="2">
-        <v>16.2</v>
+        <v>18.493200000000002</v>
       </c>
       <c r="L8" s="2">
-        <v>4.8</v>
+        <v>5.4977</v>
       </c>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>500</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2">
-        <v>33.799999999999997</v>
+        <v>38.708399999999997</v>
       </c>
       <c r="L9" s="2">
-        <v>50.9</v>
+        <v>58.2682</v>
       </c>
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3">
         <f>C8*C9</f>
         <v>250000</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="2:12">
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D11" s="3"/>
       <c r="J11" s="2" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6">
         <v>0.85</v>
       </c>
       <c r="D12" s="3"/>
       <c r="J12" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="2:12">
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3">
         <v>420</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3">
         <v>200000</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C18" s="6">
         <v>1005.309649</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3">
         <v>58</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C19" s="6">
         <v>603.185789</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G19" s="3">
         <v>186</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C20" s="6">
         <v>603.185789</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G20" s="3">
         <v>314</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C21" s="6">
         <v>1005.309649</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G21" s="3">
         <v>442</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C22" s="6">
         <f>SUM(C18:C21)</f>
         <v>3216.9908759999998</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:8">
-      <c r="B25" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="38"/>
+      <c r="B25" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="37"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3">
         <v>0.65</v>
@@ -3207,58 +1905,58 @@
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C28" s="8">
         <f>(0.85*C7*(C10-C22)+C16*C22)/1000</f>
         <v>7224.5717850711999</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" s="8">
         <v>0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C30" s="8">
         <f>C27*C28*0.8</f>
         <v>3756.777328237024</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C36" s="3">
         <v>0.65</v>
@@ -3267,30 +1965,30 @@
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3">
         <v>350</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C38" s="3">
         <f>C12*C37</f>
         <v>297.5</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C39" s="9">
         <f>-C11*(C37-G21)/C37</f>
@@ -3298,25 +1996,25 @@
       </c>
       <c r="D39" s="3"/>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" ht="14.4">
       <c r="B41" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" s="36"/>
-    </row>
-    <row r="42" spans="2:7">
+        <v>52</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="39"/>
+    </row>
+    <row r="42" spans="2:7" ht="14.4">
       <c r="B42" s="10">
         <v>1</v>
       </c>
@@ -3332,12 +2030,12 @@
         <f>D42*C18/1000</f>
         <v>422.23005258000001</v>
       </c>
-      <c r="F42" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="G42" s="36"/>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="F42" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="G42" s="39"/>
+    </row>
+    <row r="43" spans="2:7" ht="14.4">
       <c r="B43" s="10">
         <v>2</v>
       </c>
@@ -3346,19 +2044,19 @@
         <v>-1.4057142857142857E-3</v>
       </c>
       <c r="D43" s="13">
-        <f t="shared" ref="D43:D45" si="0">-MAX(MIN(210000*C43,$C$16),-420)</f>
+        <f>-MAX(MIN(210000*C43,$C$16),-420)</f>
         <v>295.2</v>
       </c>
       <c r="E43" s="13">
         <f>D43*C19/1000</f>
         <v>178.06044491279999</v>
       </c>
-      <c r="F43" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G43" s="36"/>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="F43" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="39"/>
+    </row>
+    <row r="44" spans="2:7" ht="14.4">
       <c r="B44" s="10">
         <v>3</v>
       </c>
@@ -3367,19 +2065,19 @@
         <v>-3.0857142857142889E-4</v>
       </c>
       <c r="D44" s="13">
-        <f t="shared" si="0"/>
+        <f>-MAX(MIN(210000*C44,$C$16),-420)</f>
         <v>64.800000000000068</v>
       </c>
       <c r="E44" s="13">
         <f>D44*C20/1000</f>
         <v>39.086439127200045</v>
       </c>
-      <c r="F44" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G44" s="36"/>
-    </row>
-    <row r="45" spans="2:7">
+      <c r="F44" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="39"/>
+    </row>
+    <row r="45" spans="2:7" ht="14.4">
       <c r="B45" s="10">
         <v>4</v>
       </c>
@@ -3388,21 +2086,21 @@
         <v>7.8857142857142798E-4</v>
       </c>
       <c r="D45" s="13">
-        <f t="shared" si="0"/>
+        <f>-MAX(MIN(210000*C45,$C$16),-420)</f>
         <v>-165.59999999999988</v>
       </c>
       <c r="E45" s="13">
         <f>D45*C21/1000</f>
         <v>-166.47927787439988</v>
       </c>
-      <c r="F45" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45" s="36"/>
+      <c r="F45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="39"/>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -3413,50 +2111,50 @@
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C48" s="6">
         <f>SUM(E42:E46)</f>
         <v>4013.1476587456</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C49" s="6">
         <f>(E42*(0.5*$C$9-G18)+E43*(0.5*$C$9-G19)+E44*(0.5*$C$9-G20)+E45*(0.5*$C$9-G21)+E46*(0.5*$C$9-0.5*C38))/1000</f>
         <v>480.37684031752315</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C50" s="6">
         <f>C36*C48</f>
         <v>2608.5459781846403</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C51" s="6">
         <f>C36*C49</f>
         <v>312.24494620639007</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="2:7">
@@ -3467,7 +2165,7 @@
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="2:7">
@@ -3475,7 +2173,7 @@
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C56" s="3">
         <v>0.65</v>
@@ -3484,7 +2182,7 @@
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C57" s="3">
         <f>C16/C17</f>
@@ -3494,47 +2192,47 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C58" s="3">
         <f>C11*G21/(C11+C57)</f>
         <v>260</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="2:7">
       <c r="B59" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C59" s="8">
         <f>C12*C58</f>
         <v>221</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="14.4">
       <c r="B61" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" s="36"/>
-    </row>
-    <row r="62" spans="2:7">
+        <v>52</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="39"/>
+    </row>
+    <row r="62" spans="2:7" ht="14.4">
       <c r="B62" s="10">
         <v>1</v>
       </c>
@@ -3550,54 +2248,54 @@
         <f>D62*C18/1000</f>
         <v>422.23005258000001</v>
       </c>
-      <c r="F62" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="G62" s="36"/>
-    </row>
-    <row r="63" spans="2:7">
+      <c r="F62" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="39"/>
+    </row>
+    <row r="63" spans="2:7" ht="14.4">
       <c r="B63" s="10">
         <v>2</v>
       </c>
       <c r="C63" s="12">
-        <f t="shared" ref="C63:C64" si="1">(($C$57+$C$11)*G19/$G$21)-$C$11</f>
+        <f>(($C$57+$C$11)*G19/$G$21)-$C$11</f>
         <v>-8.5384615384615382E-4</v>
       </c>
       <c r="D63" s="13">
-        <f t="shared" ref="D63:D65" si="2">-MAX(MIN(210000*C63,$C$16),-420)</f>
+        <f>-MAX(MIN(210000*C63,$C$16),-420)</f>
         <v>179.30769230769229</v>
       </c>
       <c r="E63" s="13">
-        <f t="shared" ref="E63:E65" si="3">D63*C19/1000</f>
+        <f>D63*C19/1000</f>
         <v>108.15585185838461</v>
       </c>
-      <c r="F63" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G63" s="36"/>
-    </row>
-    <row r="64" spans="2:7">
+      <c r="F63" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G63" s="39"/>
+    </row>
+    <row r="64" spans="2:7" ht="14.4">
       <c r="B64" s="10">
         <v>3</v>
       </c>
       <c r="C64" s="12">
-        <f t="shared" si="1"/>
+        <f>(($C$57+$C$11)*G20/$G$21)-$C$11</f>
         <v>6.2307692307692324E-4</v>
       </c>
       <c r="D64" s="13">
-        <f t="shared" si="2"/>
+        <f>-MAX(MIN(210000*C64,$C$16),-420)</f>
         <v>-130.84615384615387</v>
       </c>
       <c r="E64" s="13">
-        <f t="shared" si="3"/>
+        <f>D64*C20/1000</f>
         <v>-78.924540545307707</v>
       </c>
-      <c r="F64" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="G64" s="36"/>
-    </row>
-    <row r="65" spans="2:7">
+      <c r="F64" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="39"/>
+    </row>
+    <row r="65" spans="2:7" ht="14.4">
       <c r="B65" s="10">
         <v>4</v>
       </c>
@@ -3606,21 +2304,21 @@
         <v>2.1000000000000003E-3</v>
       </c>
       <c r="D65" s="13">
-        <f t="shared" si="2"/>
+        <f>-MAX(MIN(210000*C65,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E65" s="13">
-        <f t="shared" si="3"/>
+        <f>D65*C21/1000</f>
         <v>-422.23005258000001</v>
       </c>
-      <c r="F65" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G65" s="36"/>
+      <c r="F65" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G65" s="39"/>
     </row>
     <row r="66" spans="2:7">
       <c r="B66" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -3634,50 +2332,50 @@
     </row>
     <row r="68" spans="2:7">
       <c r="B68" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C68" s="6">
         <f>SUM(E62:E66)</f>
         <v>2659.1313113130768</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="2:7">
       <c r="B69" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C69" s="6">
         <f>(ABS(E62)*(0.5*C9-G18)+ABS(E63)*(0.5*C9-G19)+ABS(E64)*(G20-0.5*C9)+ABS(E65)*(G21-0.5*C9)+ABS(E66)*(0.5*C9-0.5*C59))/1000</f>
         <v>540.98053530455638</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C70" s="6">
         <f>C56*C68</f>
         <v>1728.4353523535001</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="2:7">
       <c r="B71" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C71" s="6">
         <f>C56*C69</f>
         <v>351.63734794796164</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="2:7">
@@ -3688,7 +2386,7 @@
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="2:7">
@@ -3696,7 +2394,7 @@
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C76" s="6">
         <f>0.65+(C77-0.002)*0.25/0.003</f>
@@ -3706,7 +2404,7 @@
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C77" s="3">
         <v>3.0000000000000001E-3</v>
@@ -3715,50 +2413,50 @@
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C78" s="3">
         <f>C11*G21/(C11+C77)</f>
         <v>221</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="2:7">
       <c r="B79" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C79" s="8">
         <f>C12*C78</f>
         <v>187.85</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="14"/>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:7" ht="14.4">
       <c r="B81" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F81" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G81" s="36"/>
-    </row>
-    <row r="82" spans="2:7">
+        <v>52</v>
+      </c>
+      <c r="F81" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G81" s="39"/>
+    </row>
+    <row r="82" spans="2:7" ht="14.4">
       <c r="B82" s="10">
         <v>1</v>
       </c>
@@ -3774,77 +2472,77 @@
         <f>D82*C18/1000</f>
         <v>422.23005258000001</v>
       </c>
-      <c r="F82" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="36"/>
-    </row>
-    <row r="83" spans="2:7">
+      <c r="F82" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G82" s="39"/>
+    </row>
+    <row r="83" spans="2:7" ht="14.4">
       <c r="B83" s="10">
         <v>2</v>
       </c>
       <c r="C83" s="12">
-        <f t="shared" ref="C83:C85" si="4">(($C$77+$C$11)*G19/$G$21)-$C$11</f>
+        <f>(($C$77+$C$11)*G19/$G$21)-$C$11</f>
         <v>-4.751131221719454E-4</v>
       </c>
       <c r="D83" s="13">
-        <f t="shared" ref="D83:D85" si="5">-MAX(MIN(210000*C83,$C$16),-420)</f>
+        <f>-MAX(MIN(210000*C83,$C$16),-420)</f>
         <v>99.773755656108534</v>
       </c>
       <c r="E83" s="13">
         <f>D83*C19/1000</f>
         <v>60.182111526923038</v>
       </c>
-      <c r="F83" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G83" s="36"/>
-    </row>
-    <row r="84" spans="2:7">
+      <c r="F83" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G83" s="39"/>
+    </row>
+    <row r="84" spans="2:7" ht="14.4">
       <c r="B84" s="10">
         <v>3</v>
       </c>
       <c r="C84" s="12">
-        <f t="shared" si="4"/>
+        <f>(($C$77+$C$11)*G20/$G$21)-$C$11</f>
         <v>1.2624434389140278E-3</v>
       </c>
       <c r="D84" s="13">
-        <f t="shared" si="5"/>
+        <f>-MAX(MIN(210000*C84,$C$16),-420)</f>
         <v>-265.1131221719458</v>
       </c>
       <c r="E84" s="13">
-        <f t="shared" ref="E84:E85" si="6">D84*C20/1000</f>
+        <f>D84*C20/1000</f>
         <v>-159.91246777153853</v>
       </c>
-      <c r="F84" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="G84" s="36"/>
-    </row>
-    <row r="85" spans="2:7">
+      <c r="F84" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G84" s="39"/>
+    </row>
+    <row r="85" spans="2:7" ht="14.4">
       <c r="B85" s="10">
         <v>4</v>
       </c>
       <c r="C85" s="12">
-        <f t="shared" si="4"/>
+        <f>(($C$77+$C$11)*G21/$G$21)-$C$11</f>
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D85" s="13">
-        <f t="shared" si="5"/>
+        <f>-MAX(MIN(210000*C85,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E85" s="13">
-        <f t="shared" si="6"/>
+        <f>D85*C21/1000</f>
         <v>-422.23005258000001</v>
       </c>
-      <c r="F85" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G85" s="36"/>
+      <c r="F85" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="39"/>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -3858,50 +2556,50 @@
     </row>
     <row r="88" spans="2:7">
       <c r="B88" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C88" s="6">
         <f>SUM(E82:E86)</f>
         <v>2135.6846437553845</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C89" s="6">
         <f>(ABS(E82)*(0.5*$C$9-G18)+ABS(E83)*(0.5*$C$9-G19)+ABS(E84)*(G20-0.5*$C$9)+ABS(E85)*(G21-0.5*$C$9)+ABS(E86)*(0.5*$C$9-0.5*C79))/1000</f>
         <v>525.11478939082144</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="2:7">
       <c r="B90" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C90" s="6">
         <f>C76*C88</f>
         <v>1566.1687387539487</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" spans="2:7">
       <c r="B91" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C91" s="6">
         <f>C76*C89</f>
         <v>385.08417888660244</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="2:7">
@@ -3912,7 +2610,7 @@
     </row>
     <row r="94" spans="2:7">
       <c r="B94" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="2:7">
@@ -3920,7 +2618,7 @@
     </row>
     <row r="96" spans="2:7">
       <c r="B96" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C96" s="3">
         <v>0.9</v>
@@ -3929,7 +2627,7 @@
     </row>
     <row r="97" spans="2:7">
       <c r="B97" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C97" s="3">
         <v>5.1000000000000004E-3</v>
@@ -3938,50 +2636,50 @@
     </row>
     <row r="98" spans="2:7">
       <c r="B98" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C98" s="8">
         <f>(C11*G21)/(C11+C97)</f>
         <v>163.70370370370372</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="2:7">
       <c r="B99" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C99" s="8">
         <f>C12*C98</f>
         <v>139.14814814814815</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="2:7">
       <c r="B100" s="14"/>
     </row>
-    <row r="101" spans="2:7">
+    <row r="101" spans="2:7" ht="14.4">
       <c r="B101" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G101" s="36"/>
-    </row>
-    <row r="102" spans="2:7">
+        <v>52</v>
+      </c>
+      <c r="F101" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G101" s="39"/>
+    </row>
+    <row r="102" spans="2:7" ht="14.4">
       <c r="B102" s="10">
         <v>1</v>
       </c>
@@ -3997,77 +2695,77 @@
         <f>D102*C18/1000</f>
         <v>408.95177717081003</v>
       </c>
-      <c r="F102" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G102" s="36"/>
-    </row>
-    <row r="103" spans="2:7">
+      <c r="F102" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G102" s="39"/>
+    </row>
+    <row r="103" spans="2:7" ht="14.4">
       <c r="B103" s="10">
         <v>2</v>
       </c>
       <c r="C103" s="12">
-        <f t="shared" ref="C103:C105" si="7">(($C$97+$C$11)*G19/$G$21)-$C$11</f>
+        <f>(($C$97+$C$11)*G19/$G$21)-$C$11</f>
         <v>4.0859728506787308E-4</v>
       </c>
       <c r="D103" s="13">
-        <f t="shared" ref="D103:D105" si="8">-MAX(MIN(210000*C103,$C$16),-420)</f>
+        <f>-MAX(MIN(210000*C103,$C$16),-420)</f>
         <v>-85.805429864253341</v>
       </c>
       <c r="E103" s="13">
-        <f t="shared" ref="E103:E105" si="9">D103*C19/1000</f>
+        <f>D103*C19/1000</f>
         <v>-51.756615913153816</v>
       </c>
-      <c r="F103" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="G103" s="36"/>
-    </row>
-    <row r="104" spans="2:7">
+      <c r="F103" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G103" s="39"/>
+    </row>
+    <row r="104" spans="2:7" ht="14.4">
       <c r="B104" s="10">
         <v>3</v>
       </c>
       <c r="C104" s="12">
-        <f t="shared" si="7"/>
+        <f>(($C$97+$C$11)*G20/$G$21)-$C$11</f>
         <v>2.7542986425339354E-3</v>
       </c>
       <c r="D104" s="13">
-        <f t="shared" si="8"/>
+        <f>-MAX(MIN(210000*C104,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E104" s="13">
-        <f t="shared" si="9"/>
+        <f>D104*C20/1000</f>
         <v>-253.33803137999999</v>
       </c>
-      <c r="F104" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G104" s="36"/>
-    </row>
-    <row r="105" spans="2:7">
+      <c r="F104" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G104" s="39"/>
+    </row>
+    <row r="105" spans="2:7" ht="14.4">
       <c r="B105" s="10">
         <v>4</v>
       </c>
       <c r="C105" s="12">
-        <f t="shared" si="7"/>
+        <f>(($C$97+$C$11)*G21/$G$21)-$C$11</f>
         <v>5.0999999999999995E-3</v>
       </c>
       <c r="D105" s="13">
-        <f t="shared" si="8"/>
+        <f>-MAX(MIN(210000*C105,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E105" s="13">
-        <f t="shared" si="9"/>
+        <f>D105*C21/1000</f>
         <v>-422.23005258000001</v>
       </c>
-      <c r="F105" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G105" s="36"/>
+      <c r="F105" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G105" s="39"/>
     </row>
     <row r="106" spans="2:7">
       <c r="B106" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
@@ -4081,50 +2779,50 @@
     </row>
     <row r="108" spans="2:7">
       <c r="B108" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C108" s="6">
         <f>SUM(E102:E106)</f>
         <v>1337.4900402606195</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109" spans="2:7">
       <c r="B109" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C109" s="6">
         <f>(E102*(0.5*$C$9-G18)+E103*(0.5*$C$9-G19)+E104*(0.5*$C$9-G20)+E105*(0.5*$C$9-G21)+E106*(0.5*$C$9-0.5*C99))/1000</f>
         <v>471.2487302010735</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="2:7">
       <c r="B110" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C110" s="6">
         <f>C96*C108</f>
         <v>1203.7410362345577</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="2:7">
       <c r="B111" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C111" s="6">
         <f>C96*C109</f>
         <v>424.12385718096618</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="112" spans="2:7">
@@ -4135,12 +2833,12 @@
     </row>
     <row r="114" spans="2:7">
       <c r="B114" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="2:7">
       <c r="B116" s="15" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C116" s="16">
         <v>0.9</v>
@@ -4149,30 +2847,30 @@
     </row>
     <row r="117" spans="2:7">
       <c r="B117" s="17" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C117" s="18">
         <v>76.618836993480258</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="2:7">
       <c r="B118" s="17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C118" s="18">
         <f>C12*C117</f>
         <v>65.126011444458214</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="2:7">
       <c r="B119" s="15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C119" s="18">
         <f>C11*(G21-C117)/C117</f>
@@ -4180,25 +2878,25 @@
       </c>
       <c r="D119" s="3"/>
     </row>
-    <row r="121" spans="2:7">
+    <row r="121" spans="2:7" ht="14.4">
       <c r="B121" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F121" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="G121" s="36"/>
-    </row>
-    <row r="122" spans="2:7">
+        <v>52</v>
+      </c>
+      <c r="F121" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G121" s="39"/>
+    </row>
+    <row r="122" spans="2:7" ht="14.4">
       <c r="B122" s="10">
         <v>1</v>
       </c>
@@ -4214,12 +2912,12 @@
         <f>D122*C18/1000</f>
         <v>153.90665333522173</v>
       </c>
-      <c r="F122" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="G122" s="36"/>
-    </row>
-    <row r="123" spans="2:7">
+      <c r="F122" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G122" s="39"/>
+    </row>
+    <row r="123" spans="2:7" ht="14.4">
       <c r="B123" s="10">
         <v>2</v>
       </c>
@@ -4228,19 +2926,19 @@
         <v>4.2828043585088878E-3</v>
       </c>
       <c r="D123" s="13">
-        <f t="shared" ref="D123:D125" si="10">-MAX(MIN(210000*C123,$C$16),-420)</f>
+        <f>-MAX(MIN(210000*C123,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E123" s="13">
         <f>D123*C19/1000</f>
         <v>-253.33803137999999</v>
       </c>
-      <c r="F123" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="G123" s="36"/>
-    </row>
-    <row r="124" spans="2:7">
+      <c r="F123" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G123" s="39"/>
+    </row>
+    <row r="124" spans="2:7" ht="14.4">
       <c r="B124" s="10">
         <v>3</v>
       </c>
@@ -4249,19 +2947,19 @@
         <v>9.2946267127515629E-3</v>
       </c>
       <c r="D124" s="13">
-        <f t="shared" si="10"/>
+        <f>-MAX(MIN(210000*C124,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E124" s="13">
         <f>D124*C20/1000</f>
         <v>-253.33803137999999</v>
       </c>
-      <c r="F124" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G124" s="36"/>
-    </row>
-    <row r="125" spans="2:7">
+      <c r="F124" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G124" s="39"/>
+    </row>
+    <row r="125" spans="2:7" ht="14.4">
       <c r="B125" s="10">
         <v>4</v>
       </c>
@@ -4270,21 +2968,21 @@
         <v>1.4306449066994239E-2</v>
       </c>
       <c r="D125" s="13">
-        <f t="shared" si="10"/>
+        <f>-MAX(MIN(210000*C125,$C$16),-420)</f>
         <v>-420</v>
       </c>
       <c r="E125" s="13">
         <f>D125*C21/1000</f>
         <v>-422.23005258000001</v>
       </c>
-      <c r="F125" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G125" s="36"/>
+      <c r="F125" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G125" s="39"/>
     </row>
     <row r="126" spans="2:7">
       <c r="B126" s="10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C126" s="10"/>
       <c r="D126" s="10"/>
@@ -4303,30 +3001,30 @@
     </row>
     <row r="128" spans="2:7">
       <c r="B128" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C128" s="6">
         <f>SUM(E122:E126)</f>
         <v>7.4184274467370415E-5</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E128" s="31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G128" s="20"/>
     </row>
     <row r="129" spans="2:7">
       <c r="B129" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C129" s="6">
         <f>(E122*(0.5*$C$9-G18)+E123*(0.5*$C$9-G19)+E124*(0.5*$C$9-G20)+E125*(0.5*$C$9-G21)+E126*(0.5*$C$9-0.5*C118))/1000</f>
         <v>279.13181725133677</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E129" s="19"/>
       <c r="F129" s="19"/>
@@ -4334,14 +3032,14 @@
     </row>
     <row r="130" spans="2:7">
       <c r="B130" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C130" s="6">
         <f>C116*C128</f>
         <v>6.6765847020633376E-5</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E130" s="19"/>
       <c r="F130" s="19"/>
@@ -4349,14 +3047,14 @@
     </row>
     <row r="131" spans="2:7">
       <c r="B131" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C131" s="6">
         <f>C116*C129</f>
         <v>251.21863552620309</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E131" s="19"/>
       <c r="F131" s="19"/>
@@ -4380,7 +3078,7 @@
     </row>
     <row r="134" spans="2:7">
       <c r="B134" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C134" s="19"/>
       <c r="D134" s="19"/>
@@ -4398,7 +3096,7 @@
     </row>
     <row r="136" spans="2:7">
       <c r="B136" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C136" s="3">
         <v>0.9</v>
@@ -4410,14 +3108,14 @@
     </row>
     <row r="137" spans="2:7">
       <c r="B137" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C137" s="8">
         <f>-C16*C22/1000</f>
         <v>-1351.1361679199999</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E137" s="19"/>
       <c r="F137" s="19"/>
@@ -4425,13 +3123,13 @@
     </row>
     <row r="138" spans="2:7">
       <c r="B138" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C138" s="8">
         <v>0</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E138" s="19"/>
       <c r="F138" s="19"/>
@@ -4439,14 +3137,14 @@
     </row>
     <row r="139" spans="2:7">
       <c r="B139" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C139" s="8">
         <f>C136*C137</f>
         <v>-1216.022551128</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E139" s="19"/>
       <c r="F139" s="19"/>
@@ -4454,15 +3152,15 @@
     </row>
     <row r="140" spans="2:7">
       <c r="B140" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C140" s="3">
         <v>0</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E140" s="37"/>
+        <v>42</v>
+      </c>
+      <c r="E140" s="40"/>
       <c r="F140" s="37"/>
       <c r="G140" s="20"/>
     </row>
@@ -4485,21 +3183,21 @@
     <row r="144" spans="2:7">
       <c r="B144" s="21"/>
       <c r="C144" s="21" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="E144" s="32" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F144" s="32" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="30" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C145" s="26">
         <f>C29</f>
@@ -4520,7 +3218,7 @@
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="30" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C146" s="27">
         <f>C49</f>
@@ -4541,7 +3239,7 @@
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="30" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C147" s="27">
         <f>C69</f>
@@ -4562,7 +3260,7 @@
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="30" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C148" s="27">
         <f>C89</f>
@@ -4583,7 +3281,7 @@
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="30" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C149" s="27">
         <f>C109</f>
@@ -4604,7 +3302,7 @@
     </row>
     <row r="150" spans="2:6">
       <c r="B150" s="30" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C150" s="27">
         <f>C129</f>
@@ -4625,7 +3323,7 @@
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="17" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C151" s="22">
         <f>C138</f>
@@ -4646,7 +3344,7 @@
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="28" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C152" s="29">
         <f>-C150</f>
@@ -4667,7 +3365,7 @@
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="28" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C153" s="29">
         <f>-C149</f>
@@ -4688,7 +3386,7 @@
     </row>
     <row r="154" spans="2:6">
       <c r="B154" s="28" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C154" s="29">
         <f>-C148</f>
@@ -4709,7 +3407,7 @@
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="28" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C155" s="29">
         <f>-C147</f>
@@ -4730,7 +3428,7 @@
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="28" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C156" s="29">
         <f>-C146</f>
@@ -4751,7 +3449,7 @@
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="28" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C157" s="29">
         <f>-C145</f>
@@ -4824,35 +3522,34 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F124:G124"/>
     <mergeCell ref="E140:F140"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F104:G104"/>
     <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="F84:G84"/>
     <mergeCell ref="F85:G85"/>
     <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F121:G121"/>
     <mergeCell ref="F102:G102"/>
-    <mergeCell ref="F104:G104"/>
     <mergeCell ref="F105:G105"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F43:G43"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
